--- a/experiment/ELAN_bestx8/results_HUTCN_ELAN_bestx8.xlsx
+++ b/experiment/ELAN_bestx8/results_HUTCN_ELAN_bestx8.xlsx
@@ -533,7 +533,7 @@
       <c r="D5" t="n">
         <v>0.0062</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>25.29</v>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       <c r="D39" t="n">
         <v>0.00516</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" t="n">
         <v>27.424</v>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       <c r="D41" t="n">
         <v>0.00515</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" t="n">
         <v>27.397</v>
       </c>
     </row>
